--- a/problems.xlsx
+++ b/problems.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="49">
   <si>
     <t>Easy</t>
   </si>
@@ -164,6 +164,9 @@
   </si>
   <si>
     <t>find intersection node of 2 lists</t>
+  </si>
+  <si>
+    <t>Given an array of numbers and a number k, determine if there are three entries in the array which add up to the specified number k</t>
   </si>
 </sst>
 </file>
@@ -518,7 +521,7 @@
   <dimension ref="A1:D144"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="65.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="120.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="126.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1514,6 +1517,9 @@
       <c r="B144" t="s">
         <v>0</v>
       </c>
+      <c r="C144" t="s">
+        <v>48</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
